--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,123 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4170489</v>
-      </c>
-      <c r="B3" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tureborg, 350 m OSO om Sjukhemmet Kapelle, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>320753.8052519502</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6470739.938908488</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2005-09-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2005-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>alskog, skogskärr</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,342 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130084656</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97488</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>320894</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6470728</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130084801</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96051</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>320894</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6470728</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130084666</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97436</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>320894</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6470728</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97504</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96067</v>
+        <v>96069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97452</v>
+        <v>97454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96069</v>
+        <v>96156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97593</v>
+        <v>97630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Helene Jacobson, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96156</v>
+        <v>96193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Helene Jacobson, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97541</v>
+        <v>97578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Helene Jacobson, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97630</v>
+        <v>97643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96193</v>
+        <v>96206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97578</v>
+        <v>97591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97643</v>
+        <v>97644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96206</v>
+        <v>96207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97591</v>
+        <v>97592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97644</v>
+        <v>97647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96207</v>
+        <v>96210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97592</v>
+        <v>97595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>97647</v>
+        <v>97656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>96210</v>
+        <v>96219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>130084666</v>
       </c>
       <c r="B5" t="n">
-        <v>97595</v>
+        <v>97604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,15 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130084656</v>
+        <v>4170489</v>
       </c>
       <c r="B3" t="n">
-        <v>97680</v>
+        <v>95510</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,41 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+          <t>Tureborg, 350 m OSO om Sjukhemmet Kapelle, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320894</v>
+        <v>320753.8052519502</v>
       </c>
       <c r="R3" t="n">
-        <v>6470728</v>
+        <v>6470739.938908488</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2005-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2005-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,29 +886,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>alskog, skogskärr</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Christina Sandblom</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130084801</v>
+        <v>130084656</v>
       </c>
       <c r="B4" t="n">
-        <v>96243</v>
+        <v>97680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130084666</v>
+        <v>130084801</v>
       </c>
       <c r="B5" t="n">
-        <v>97628</v>
+        <v>96243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1126,6 +1131,118 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130084666</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>320894</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6470728</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Jacobson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helene Jacobson, Christina Sandblom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4219959</v>
+        <v>130084666</v>
       </c>
       <c r="B2" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tureborg, 350 m OSO om Sjukhemmet Kapelle, Boh</t>
+          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320753.8052519502</v>
+        <v>320894</v>
       </c>
       <c r="R2" t="n">
-        <v>6470739.938908488</v>
+        <v>6470728</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-09-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-09-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +768,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Alkärr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Helene Jacobson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Helene Jacobson, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4170489</v>
+        <v>130084656</v>
       </c>
       <c r="B3" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tureborg, 350 m OSO om Sjukhemmet Kapelle, Boh</t>
+          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320753.8052519502</v>
+        <v>320894</v>
       </c>
       <c r="R3" t="n">
-        <v>6470739.938908488</v>
+        <v>6470728</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-09-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-09-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,33 +880,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>alskog, skogskärr</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Helene Jacobson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Helene Jacobson, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130084656</v>
+        <v>130084801</v>
       </c>
       <c r="B4" t="n">
-        <v>97680</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130084801</v>
+        <v>4170489</v>
       </c>
       <c r="B5" t="n">
-        <v>96243</v>
+        <v>97977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,41 +1022,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>221944</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+          <t>Tureborg, 350 m OSO om Sjukhemmet Kapelle, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320894</v>
+        <v>320754</v>
       </c>
       <c r="R5" t="n">
-        <v>6470728</v>
+        <v>6470740</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,22 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2005-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2005-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,29 +1086,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>alskog, skogskärr</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Christina Sandblom</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130084666</v>
+        <v>4219959</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,41 +1120,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timanstorpet, Alkärr 100 m VSV om vattenreservoaren, Boh</t>
+          <t>Tureborg, 350 m OSO om Sjukhemmet Kapelle, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320894</v>
+        <v>320754</v>
       </c>
       <c r="R6" t="n">
-        <v>6470728</v>
+        <v>6470740</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2005-09-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2005-09-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,19 +1188,23 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Alkärr</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Christina Sandblom</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62048-2024 artfynd.xlsx
+++ b/artfynd/A 62048-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084801</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4170489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,8 +1233,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4219959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>